--- a/actualizacion/enlaces.xlsx
+++ b/actualizacion/enlaces.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\CH_projects\SDIS\COLJ\tablero-calidad-colj\actualizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8759A72C-FE3B-4282-A135-B81DBF3B7BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20D3A75-8C73-4757-B28A-8BE64ED88239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Enlaces del tablero COLJ</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Gemini Notebook 2026</t>
+  </si>
+  <si>
+    <t>Excel de seguimiento de los COLJ</t>
+  </si>
+  <si>
+    <t>Excel vinculado al forms de los COLJ</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/1IxTTkF4sZgHvKNDGGJX9f1eLetgUrbPtSoYWHoIMD3s/edit?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -461,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -494,67 +503,78 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -563,11 +583,12 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="https://sdisgovco.sharepoint.com/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Forms/AllItems.aspx?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=GnCWLh&amp;or=WORD%2DWEB%2EBODY%2ENT&amp;ct=1787615071953&amp;CID=ab08e4f8%2Db68c%2D4040%2Db7c4%2Dad5f5470a599&amp;FolderCTID=0x012000F3947AFB90C3E34881371E69DC98F757&amp;id=%2Fsites%2FSubdireccindeJuventudPoliticaPblica%2FDocumentos%20compartidos%2FInstancias%20de%20participaci%C3%B3n%2FCOLJ" xr:uid="{9DEC7A09-7042-4940-86EF-791B96B76BED}"/>
-    <hyperlink ref="C6" r:id="rId2" xr:uid="{2119B8F4-AF1D-4FAB-B2B0-6185EDD07DBE}"/>
-    <hyperlink ref="C7" r:id="rId3" xr:uid="{911C624D-5B5C-4BBA-A00C-D527DC92DD54}"/>
-    <hyperlink ref="C8" r:id="rId4" xr:uid="{C87C6B01-CF93-44AA-9EE3-F727F3019002}"/>
-    <hyperlink ref="C10" r:id="rId5" xr:uid="{90B37D02-675E-485A-8A70-67D3E05C2F1C}"/>
+    <hyperlink ref="C6" r:id="rId1" display="https://sdisgovco.sharepoint.com/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Forms/AllItems.aspx?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=GnCWLh&amp;or=WORD%2DWEB%2EBODY%2ENT&amp;ct=1787615071953&amp;CID=ab08e4f8%2Db68c%2D4040%2Db7c4%2Dad5f5470a599&amp;FolderCTID=0x012000F3947AFB90C3E34881371E69DC98F757&amp;id=%2Fsites%2FSubdireccindeJuventudPoliticaPblica%2FDocumentos%20compartidos%2FInstancias%20de%20participaci%C3%B3n%2FCOLJ" xr:uid="{9DEC7A09-7042-4940-86EF-791B96B76BED}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{2119B8F4-AF1D-4FAB-B2B0-6185EDD07DBE}"/>
+    <hyperlink ref="C8" r:id="rId3" xr:uid="{911C624D-5B5C-4BBA-A00C-D527DC92DD54}"/>
+    <hyperlink ref="C9" r:id="rId4" xr:uid="{C87C6B01-CF93-44AA-9EE3-F727F3019002}"/>
+    <hyperlink ref="C11" r:id="rId5" xr:uid="{90B37D02-675E-485A-8A70-67D3E05C2F1C}"/>
+    <hyperlink ref="C5" r:id="rId6" xr:uid="{ED939714-8AE9-46D9-A828-42AEF9E56D37}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/actualizacion/enlaces.xlsx
+++ b/actualizacion/enlaces.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\CH_projects\SDIS\COLJ\tablero-calidad-colj\actualizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20D3A75-8C73-4757-B28A-8BE64ED88239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602E42C0-E168-4618-8FD8-9E0812EA5957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Enlaces del tablero COLJ</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>https://docs.google.com/spreadsheets/d/1IxTTkF4sZgHvKNDGGJX9f1eLetgUrbPtSoYWHoIMD3s/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/forms/d/e/1FAIpQLSeB9bHu8dLqEF40sYUGJoE5_Ah765P8QL0o70PQcOw2tG8UXg/viewform</t>
+  </si>
+  <si>
+    <t>Formulario de seguimiento</t>
+  </si>
+  <si>
+    <t>Formulario en Forms de seguimiento de los COLJ</t>
   </si>
 </sst>
 </file>
@@ -470,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -503,78 +512,89 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -583,12 +603,13 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" display="https://sdisgovco.sharepoint.com/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Forms/AllItems.aspx?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=GnCWLh&amp;or=WORD%2DWEB%2EBODY%2ENT&amp;ct=1787615071953&amp;CID=ab08e4f8%2Db68c%2D4040%2Db7c4%2Dad5f5470a599&amp;FolderCTID=0x012000F3947AFB90C3E34881371E69DC98F757&amp;id=%2Fsites%2FSubdireccindeJuventudPoliticaPblica%2FDocumentos%20compartidos%2FInstancias%20de%20participaci%C3%B3n%2FCOLJ" xr:uid="{9DEC7A09-7042-4940-86EF-791B96B76BED}"/>
-    <hyperlink ref="C7" r:id="rId2" xr:uid="{2119B8F4-AF1D-4FAB-B2B0-6185EDD07DBE}"/>
-    <hyperlink ref="C8" r:id="rId3" xr:uid="{911C624D-5B5C-4BBA-A00C-D527DC92DD54}"/>
-    <hyperlink ref="C9" r:id="rId4" xr:uid="{C87C6B01-CF93-44AA-9EE3-F727F3019002}"/>
-    <hyperlink ref="C11" r:id="rId5" xr:uid="{90B37D02-675E-485A-8A70-67D3E05C2F1C}"/>
-    <hyperlink ref="C5" r:id="rId6" xr:uid="{ED939714-8AE9-46D9-A828-42AEF9E56D37}"/>
+    <hyperlink ref="C7" r:id="rId1" display="https://sdisgovco.sharepoint.com/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Forms/AllItems.aspx?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=GnCWLh&amp;or=WORD%2DWEB%2EBODY%2ENT&amp;ct=1787615071953&amp;CID=ab08e4f8%2Db68c%2D4040%2Db7c4%2Dad5f5470a599&amp;FolderCTID=0x012000F3947AFB90C3E34881371E69DC98F757&amp;id=%2Fsites%2FSubdireccindeJuventudPoliticaPblica%2FDocumentos%20compartidos%2FInstancias%20de%20participaci%C3%B3n%2FCOLJ" xr:uid="{9DEC7A09-7042-4940-86EF-791B96B76BED}"/>
+    <hyperlink ref="C8" r:id="rId2" xr:uid="{2119B8F4-AF1D-4FAB-B2B0-6185EDD07DBE}"/>
+    <hyperlink ref="C9" r:id="rId3" xr:uid="{911C624D-5B5C-4BBA-A00C-D527DC92DD54}"/>
+    <hyperlink ref="C10" r:id="rId4" xr:uid="{C87C6B01-CF93-44AA-9EE3-F727F3019002}"/>
+    <hyperlink ref="C12" r:id="rId5" xr:uid="{90B37D02-675E-485A-8A70-67D3E05C2F1C}"/>
+    <hyperlink ref="C6" r:id="rId6" xr:uid="{ED939714-8AE9-46D9-A828-42AEF9E56D37}"/>
+    <hyperlink ref="C5" r:id="rId7" xr:uid="{FCCCC7A8-B683-40AA-BC10-D7D1CE2991DC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/actualizacion/enlaces.xlsx
+++ b/actualizacion/enlaces.xlsx
@@ -1,149 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\CH_projects\SDIS\COLJ\tablero-calidad-colj\actualizacion\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602E42C0-E168-4618-8FD8-9E0812EA5957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Enlaces" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enlaces" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
-  <si>
-    <t>Enlaces del tablero COLJ</t>
-  </si>
-  <si>
-    <t>Edita esta hoja para agregar, quitar o corregir un enlace. Después vuelve a correr programas/generar_tablero_calidad_colj.py y la página se actualiza. Las filas sin link salen marcadas como pendientes; las filas sin nombre se ignoran.</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Detalle</t>
-  </si>
-  <si>
-    <t>Link</t>
-  </si>
-  <si>
-    <t>SharePoint</t>
-  </si>
-  <si>
-    <t>Carpeta institucional donde se archivan actas y planillas.</t>
-  </si>
-  <si>
-    <t>Google Drive</t>
-  </si>
-  <si>
-    <t>Carpeta de trabajo con lo que llega por el formulario.</t>
-  </si>
-  <si>
-    <t>Sesiones y asistencia de la vigencia 2024.</t>
-  </si>
-  <si>
-    <t>https://sdisgovco.sharepoint.com/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Forms/AllItems.aspx?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=GnCWLh&amp;or=WORD%2DWEB%2EBODY%2ENT&amp;ct=1787615071953&amp;CID=ab08e4f8%2Db68c%2D4040%2Db7c4%2Dad5f5470a599&amp;FolderCTID=0x012000F3947AFB90C3E34881371E69DC98F757&amp;id=%2Fsites%2FSubdireccindeJuventudPoliticaPblica%2FDocumentos%20compartidos%2FInstancias%20de%20participaci%C3%B3n%2FCOLJ</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/drive/folders/1i3kRMMRAIsXNRJ-LoswLnmaOrHHqJbqw</t>
-  </si>
-  <si>
-    <t>https://notebook.google.com/notebook/64fa8e0d-65b9-4add-bea5-49fb8f2bc6fc</t>
-  </si>
-  <si>
-    <t>Gemini Notebook 2024</t>
-  </si>
-  <si>
-    <t>Gemini Notebook 2025</t>
-  </si>
-  <si>
-    <t>Cuadernos con las actas sistematizadas por año. Chat con IA.</t>
-  </si>
-  <si>
-    <t>https://notebook.google.com/notebook/41666052-3c47-45db-992d-b446900a05c8</t>
-  </si>
-  <si>
-    <t>https://notebook.google.com/notebook/7094985f-40a5-4925-bb33-e1b7f9124c97</t>
-  </si>
-  <si>
-    <t>Tablero Power BI Hackaton 2025</t>
-  </si>
-  <si>
-    <t>https://app.powerbi.com/view?r=eyJrIjoiZjVkMDBlMDUtM2Q3Zi00N2EzLTkwMGEtMjQwMjA5MTkyYjE4IiwidCI6ImIzZTMwODA4LWU5YTgtNGYyYS05YmMxLWE3NjBhZTkxMGNmNSIsImMiOjR9</t>
-  </si>
-  <si>
-    <t>Gemini Notebook 2026</t>
-  </si>
-  <si>
-    <t>Excel de seguimiento de los COLJ</t>
-  </si>
-  <si>
-    <t>Excel vinculado al forms de los COLJ</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/1IxTTkF4sZgHvKNDGGJX9f1eLetgUrbPtSoYWHoIMD3s/edit?usp=sharing</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/forms/d/e/1FAIpQLSeB9bHu8dLqEF40sYUGJoE5_Ah765P8QL0o70PQcOw2tG8UXg/viewform</t>
-  </si>
-  <si>
-    <t>Formulario de seguimiento</t>
-  </si>
-  <si>
-    <t>Formulario en Forms de seguimiento de los COLJ</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2F3E3C"/>
       <sz val="14"/>
-      <color rgb="FF2F3E3C"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF83766C"/>
       <sz val="9"/>
-      <color rgb="FF83766C"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -165,32 +74,91 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -478,124 +446,185 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="62" customWidth="1"/>
-    <col min="3" max="3" width="58" customWidth="1"/>
+    <col width="30" customWidth="1" style="5" min="1" max="1"/>
+    <col width="62" customWidth="1" style="5" min="2" max="2"/>
+    <col width="58" customWidth="1" style="5" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
+    <row r="1" ht="18.75" customHeight="1" s="5">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Enlaces del tablero COLJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1" s="5">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Edita esta hoja para agregar, quitar o corregir un enlace. Después vuelve a correr programas/generar_tablero_calidad_colj.py y la página se actualiza. Las filas sin link salen marcadas como pendientes; las filas sin nombre se ignoran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Formulario de seguimiento</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Formulario en Forms de seguimiento de los COLJ</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSeB9bHu8dLqEF40sYUGJoE5_Ah765P8QL0o70PQcOw2tG8UXg/viewform</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Excel de seguimiento de los COLJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Excel vinculado al forms de los COLJ</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/spreadsheets/d/1IxTTkF4sZgHvKNDGGJX9f1eLetgUrbPtSoYWHoIMD3s/edit?usp=sharing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SharePoint</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Carpeta institucional donde se archivan actas y planillas.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://sdisgovco.sharepoint.com/:f:/r/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Instancias%20de%20participaci%C3%B3n/COLJ?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=6gbP04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Google Drive</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Carpeta de trabajo con lo que llega por el formulario.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1i3kRMMRAIsXNRJ-LoswLnmaOrHHqJbqw</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gemini Notebook 2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cuadernos con las actas sistematizadas por año. Chat con IA.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://notebook.google.com/notebook/64fa8e0d-65b9-4add-bea5-49fb8f2bc6fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gemini Notebook 2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cuadernos con las actas sistematizadas por año. Chat con IA.</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://notebook.google.com/notebook/41666052-3c47-45db-992d-b446900a05c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gemini Notebook 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cuadernos con las actas sistematizadas por año. Chat con IA.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>https://notebook.google.com/notebook/7094985f-40a5-4925-bb33-e1b7f9124c97</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tablero Power BI Hackaton 2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sesiones y asistencia de la vigencia 2024.</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>https://app.powerbi.com/view?r=eyJrIjoiZjVkMDBlMDUtM2Q3Zi00N2EzLTkwMGEtMjQwMjA5MTkyYjE4IiwidCI6ImIzZTMwODA4LWU5YTgtNGYyYS05YmMxLWE3NjBhZTkxMGNmNSIsImMiOjR9</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -603,13 +632,13 @@
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" display="https://sdisgovco.sharepoint.com/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Forms/AllItems.aspx?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=GnCWLh&amp;or=WORD%2DWEB%2EBODY%2ENT&amp;ct=1787615071953&amp;CID=ab08e4f8%2Db68c%2D4040%2Db7c4%2Dad5f5470a599&amp;FolderCTID=0x012000F3947AFB90C3E34881371E69DC98F757&amp;id=%2Fsites%2FSubdireccindeJuventudPoliticaPblica%2FDocumentos%20compartidos%2FInstancias%20de%20participaci%C3%B3n%2FCOLJ" xr:uid="{9DEC7A09-7042-4940-86EF-791B96B76BED}"/>
-    <hyperlink ref="C8" r:id="rId2" xr:uid="{2119B8F4-AF1D-4FAB-B2B0-6185EDD07DBE}"/>
-    <hyperlink ref="C9" r:id="rId3" xr:uid="{911C624D-5B5C-4BBA-A00C-D527DC92DD54}"/>
-    <hyperlink ref="C10" r:id="rId4" xr:uid="{C87C6B01-CF93-44AA-9EE3-F727F3019002}"/>
-    <hyperlink ref="C12" r:id="rId5" xr:uid="{90B37D02-675E-485A-8A70-67D3E05C2F1C}"/>
-    <hyperlink ref="C6" r:id="rId6" xr:uid="{ED939714-8AE9-46D9-A828-42AEF9E56D37}"/>
-    <hyperlink ref="C5" r:id="rId7" xr:uid="{FCCCC7A8-B683-40AA-BC10-D7D1CE2991DC}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" display="https://sdisgovco.sharepoint.com/sites/SubdireccindeJuventudPoliticaPblica/Documentos%20compartidos/Forms/AllItems.aspx?d=w51f1c999a8b54dafb1aba57e1b1c1ef7&amp;csf=1&amp;web=1&amp;e=GnCWLh&amp;or=WORD%2DWEB%2EBODY%2ENT&amp;ct=1787615071953&amp;CID=ab08e4f8%2Db68c%2D4040%2Db7c4%2Dad5f5470a599&amp;FolderCTID=0x012000F3947AFB90C3E34881371E69DC98F757&amp;id=%2Fsites%2FSubdireccindeJuventudPoliticaPblica%2FDocumentos%20compartidos%2FInstancias%20de%20participaci%C3%B3n%2FCOLJ" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/actualizacion/enlaces.xlsx
+++ b/actualizacion/enlaces.xlsx
@@ -76,7 +76,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -473,7 +474,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="5">
       <c r="A12" t="inlineStr">
         <is>
           <t>Tablero Power BI Hackaton 2025</t>
@@ -624,6 +624,23 @@
       <c r="C12" s="3" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/view?r=eyJrIjoiZjVkMDBlMDUtM2Q3Zi00N2EzLTkwMGEtMjQwMjA5MTkyYjE4IiwidCI6ImIzZTMwODA4LWU5YTgtNGYyYS05YmMxLWE3NjBhZTkxMGNmNSIsImMiOjR9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Decreto 647 de 2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Abre en los artículos de los COLJ (133 a 138): funciones, integrantes, secretaría técnica y sesiones.</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.alcaldiabogota.gov.co/sisjur/normas/Norma1.jsp?i=191867#133</t>
         </is>
       </c>
     </row>
